--- a/src/data/excel/dec.xlsx
+++ b/src/data/excel/dec.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VNC\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Study\Chandru\c\My Learnings\React js\React Projects\college\src\data\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -35,13 +35,7 @@
     <t>holiday</t>
   </si>
   <si>
-    <t>Krishna Jayanthi</t>
-  </si>
-  <si>
-    <t>Vinayagar Chaturthi</t>
-  </si>
-  <si>
-    <t>Miladi Nabi</t>
+    <t>Christmas</t>
   </si>
 </sst>
 </file>
@@ -409,7 +403,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -425,10 +419,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>0</v>
-      </c>
-      <c r="C7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -436,7 +427,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -444,7 +435,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -468,7 +459,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -476,7 +467,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -484,7 +475,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -492,7 +483,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -500,7 +491,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -524,7 +515,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -532,10 +523,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="1">
-        <v>0</v>
-      </c>
-      <c r="C20" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -543,7 +531,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -551,7 +539,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -559,7 +547,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -583,7 +571,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="C26" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -591,7 +582,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -599,7 +590,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -607,9 +598,6 @@
         <v>28</v>
       </c>
       <c r="B29" s="1">
-        <v>0</v>
-      </c>
-      <c r="C29" t="s">
         <v>5</v>
       </c>
     </row>
@@ -618,7 +606,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -630,8 +618,12 @@
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
